--- a/www/flightdata/xlsx/eoss-295.xlsx
+++ b/www/flightdata/xlsx/eoss-295.xlsx
@@ -2961,7 +2961,7 @@
         <v>33558.78</v>
       </c>
       <c r="I2">
-        <v>515</v>
+        <v>357</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
